--- a/test/fixtures/proba-adatbekero-kitoltott.xlsx
+++ b/test/fixtures/proba-adatbekero-kitoltott.xlsx
@@ -644,15 +644,6 @@
 (magyarul: Korábbi utca/cím)
 Optional / Nem kötelező
 Street name and house number of the last address abroad, in this one cell.</t>
-      </text>
-    </comment>
-    <comment ref="AX2" authorId="0" shapeId="0">
-      <text>
-        <t>Means of Transport
-(magyarul: Hazautazás módja)
-Optional / Nem kötelező
-How the employee will travel home when the stay expires. English is fine – the Hungarian form comes from the dictionary.
-Example: by car, by bus, by plane</t>
       </text>
     </comment>
   </commentList>
@@ -985,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1031,7 +1022,7 @@
     <col width="21" customWidth="1" min="46" max="46"/>
     <col width="18" customWidth="1" min="47" max="47"/>
     <col width="21" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="50"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1" ht="30" customHeight="1">
@@ -1280,11 +1271,6 @@
           <t>previous_street</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>transport_type</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1532,11 +1518,6 @@
           <t>Previous Address (Street)</t>
         </is>
       </c>
-      <c r="AX2" s="3" t="inlineStr">
-        <is>
-          <t>Means of Transport</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1778,11 +1759,6 @@
           <t>Trg Slobode 4</t>
         </is>
       </c>
-      <c r="AX3" s="5" t="inlineStr">
-        <is>
-          <t>bus</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -2026,11 +2002,6 @@
       <c r="AW4" s="5" t="inlineStr">
         <is>
           <t>Shevchenka Street 21</t>
-        </is>
-      </c>
-      <c r="AX4" s="5" t="inlineStr">
-        <is>
-          <t>bus</t>
         </is>
       </c>
     </row>
@@ -2264,11 +2235,6 @@
       <c r="AW5" s="5" t="inlineStr">
         <is>
           <t>Osmena Boulevard 118</t>
-        </is>
-      </c>
-      <c r="AX5" s="5" t="inlineStr">
-        <is>
-          <t>airplane</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2288,6 @@
       <c r="AU6" s="5" t="n"/>
       <c r="AV6" s="5" t="n"/>
       <c r="AW6" s="5" t="n"/>
-      <c r="AX6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -2374,7 +2339,6 @@
       <c r="AU7" s="5" t="n"/>
       <c r="AV7" s="5" t="n"/>
       <c r="AW7" s="5" t="n"/>
-      <c r="AX7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -2426,7 +2390,6 @@
       <c r="AU8" s="5" t="n"/>
       <c r="AV8" s="5" t="n"/>
       <c r="AW8" s="5" t="n"/>
-      <c r="AX8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -2478,7 +2441,6 @@
       <c r="AU9" s="5" t="n"/>
       <c r="AV9" s="5" t="n"/>
       <c r="AW9" s="5" t="n"/>
-      <c r="AX9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -2530,7 +2492,6 @@
       <c r="AU10" s="5" t="n"/>
       <c r="AV10" s="5" t="n"/>
       <c r="AW10" s="5" t="n"/>
-      <c r="AX10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -2582,7 +2543,6 @@
       <c r="AU11" s="5" t="n"/>
       <c r="AV11" s="5" t="n"/>
       <c r="AW11" s="5" t="n"/>
-      <c r="AX11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -2634,7 +2594,6 @@
       <c r="AU12" s="5" t="n"/>
       <c r="AV12" s="5" t="n"/>
       <c r="AW12" s="5" t="n"/>
-      <c r="AX12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -2686,7 +2645,6 @@
       <c r="AU13" s="5" t="n"/>
       <c r="AV13" s="5" t="n"/>
       <c r="AW13" s="5" t="n"/>
-      <c r="AX13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -2738,7 +2696,6 @@
       <c r="AU14" s="5" t="n"/>
       <c r="AV14" s="5" t="n"/>
       <c r="AW14" s="5" t="n"/>
-      <c r="AX14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -2790,7 +2747,6 @@
       <c r="AU15" s="5" t="n"/>
       <c r="AV15" s="5" t="n"/>
       <c r="AW15" s="5" t="n"/>
-      <c r="AX15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -2842,7 +2798,6 @@
       <c r="AU16" s="5" t="n"/>
       <c r="AV16" s="5" t="n"/>
       <c r="AW16" s="5" t="n"/>
-      <c r="AX16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -2894,7 +2849,6 @@
       <c r="AU17" s="5" t="n"/>
       <c r="AV17" s="5" t="n"/>
       <c r="AW17" s="5" t="n"/>
-      <c r="AX17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -2946,7 +2900,6 @@
       <c r="AU18" s="5" t="n"/>
       <c r="AV18" s="5" t="n"/>
       <c r="AW18" s="5" t="n"/>
-      <c r="AX18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -2998,7 +2951,6 @@
       <c r="AU19" s="5" t="n"/>
       <c r="AV19" s="5" t="n"/>
       <c r="AW19" s="5" t="n"/>
-      <c r="AX19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -3050,7 +3002,6 @@
       <c r="AU20" s="5" t="n"/>
       <c r="AV20" s="5" t="n"/>
       <c r="AW20" s="5" t="n"/>
-      <c r="AX20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -3102,7 +3053,6 @@
       <c r="AU21" s="5" t="n"/>
       <c r="AV21" s="5" t="n"/>
       <c r="AW21" s="5" t="n"/>
-      <c r="AX21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -3154,7 +3104,6 @@
       <c r="AU22" s="5" t="n"/>
       <c r="AV22" s="5" t="n"/>
       <c r="AW22" s="5" t="n"/>
-      <c r="AX22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -3206,7 +3155,6 @@
       <c r="AU23" s="5" t="n"/>
       <c r="AV23" s="5" t="n"/>
       <c r="AW23" s="5" t="n"/>
-      <c r="AX23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -3258,7 +3206,6 @@
       <c r="AU24" s="5" t="n"/>
       <c r="AV24" s="5" t="n"/>
       <c r="AW24" s="5" t="n"/>
-      <c r="AX24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -3310,7 +3257,6 @@
       <c r="AU25" s="5" t="n"/>
       <c r="AV25" s="5" t="n"/>
       <c r="AW25" s="5" t="n"/>
-      <c r="AX25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -3362,7 +3308,6 @@
       <c r="AU26" s="5" t="n"/>
       <c r="AV26" s="5" t="n"/>
       <c r="AW26" s="5" t="n"/>
-      <c r="AX26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -3414,7 +3359,6 @@
       <c r="AU27" s="5" t="n"/>
       <c r="AV27" s="5" t="n"/>
       <c r="AW27" s="5" t="n"/>
-      <c r="AX27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -3466,7 +3410,6 @@
       <c r="AU28" s="5" t="n"/>
       <c r="AV28" s="5" t="n"/>
       <c r="AW28" s="5" t="n"/>
-      <c r="AX28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -3518,7 +3461,6 @@
       <c r="AU29" s="5" t="n"/>
       <c r="AV29" s="5" t="n"/>
       <c r="AW29" s="5" t="n"/>
-      <c r="AX29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -3570,7 +3512,6 @@
       <c r="AU30" s="5" t="n"/>
       <c r="AV30" s="5" t="n"/>
       <c r="AW30" s="5" t="n"/>
-      <c r="AX30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -3622,7 +3563,6 @@
       <c r="AU31" s="5" t="n"/>
       <c r="AV31" s="5" t="n"/>
       <c r="AW31" s="5" t="n"/>
-      <c r="AX31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -3674,10 +3614,9 @@
       <c r="AU32" s="5" t="n"/>
       <c r="AV32" s="5" t="n"/>
       <c r="AW32" s="5" t="n"/>
-      <c r="AX32" s="5" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="AmmIXoYzsLSSNkbil79ARA==" formatRows="1" sort="1" spinCount="100000" hashValue="mR2QbeNuTiEGF/pLyY6BWBZeswby0+VGFFqpNkVzRlrJ9XaYWVfFSz/rdG/tB7Eo7C/ccM0p/28Obfsa3wIDWA=="/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="lWj7B3mtRAI2vRJgBSnJWw==" formatRows="1" sort="1" spinCount="100000" hashValue="u+5RPHqC7hBPPodKMKUjdmHMxkaThamhILljXQsu28BZY56RNGpk8mUA2EauSYqwleZ3NnMryDKFnBbTOPkZ4g=="/>
   <dataValidations count="5">
     <dataValidation sqref="AP3:AP202" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nem a listából választott érték" error="Válassz a legördülő listából, vagy hagyd üresen." type="list" errorStyle="warning">
       <formula1>"none,primary,secondary,tertiary"</formula1>
@@ -3707,7 +3646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4802,25 +4741,6 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="10" t="inlineStr"/>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>transport_type</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Hazautazás módja</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Hazautazás</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
